--- a/translations/welsh-translations/14-compliance-submit-error.xlsx
+++ b/translations/welsh-translations/14-compliance-submit-error.xlsx
@@ -618,7 +618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
